--- a/new original/_Lang_Chinese/Lang/CN/Game/SpawnList.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Game/SpawnList.xlsx
@@ -29,7 +29,7 @@
     <t xml:space="preserve">all</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.267</t>
+    <t xml:space="preserve">EA 23.282</t>
   </si>
   <si>
     <t xml:space="preserve">chara</t>

--- a/new original/_Lang_Chinese/Lang/CN/Game/SpawnList.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Game/SpawnList.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="73">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -29,7 +29,7 @@
     <t xml:space="preserve">all</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.282</t>
+    <t xml:space="preserve">EA 23.287</t>
   </si>
   <si>
     <t xml:space="preserve">chara</t>
@@ -113,34 +113,34 @@
     <t xml:space="preserve">shop_gun</t>
   </si>
   <si>
+    <t xml:space="preserve">shop_magic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shop_healer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shop_furniture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shop_drink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shop_fruit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shop_book</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shop_seeker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shop_booze</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shop_meat</t>
+  </si>
+  <si>
     <t xml:space="preserve">shop_bread</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shop_magic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shop_healer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shop_furniture</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shop_drink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shop_fruit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shop_book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shop_seeker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shop_booze</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shop_meat</t>
   </si>
   <si>
     <t xml:space="preserve">shop_sweet</t>
@@ -575,7 +575,7 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="C32"/>
     </row>
@@ -584,7 +584,7 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="C33"/>
     </row>
@@ -620,7 +620,7 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="C37"/>
     </row>
@@ -629,7 +629,7 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="C38"/>
     </row>
@@ -653,25 +653,25 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="C41"/>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="C42"/>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B43" t="s">
         <v>52</v>
@@ -680,7 +680,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B44" t="s">
         <v>52</v>
@@ -689,7 +689,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B45" t="s">
         <v>52</v>
@@ -698,7 +698,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B46" t="s">
         <v>52</v>
@@ -707,48 +707,39 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="C47"/>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C48"/>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C49"/>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C50"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="s">
-        <v>51</v>
-      </c>
-      <c r="B51" t="s">
-        <v>72</v>
-      </c>
-      <c r="C51"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:C2"/>

--- a/new original/_Lang_Chinese/Lang/CN/Game/SpawnList.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Game/SpawnList.xlsx
@@ -29,7 +29,7 @@
     <t xml:space="preserve">all</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.287</t>
+    <t xml:space="preserve">EA 23.295</t>
   </si>
   <si>
     <t xml:space="preserve">chara</t>

--- a/new original/_Lang_Chinese/Lang/CN/Game/SpawnList.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Game/SpawnList.xlsx
@@ -29,7 +29,7 @@
     <t xml:space="preserve">all</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.295</t>
+    <t xml:space="preserve">EA 23.287</t>
   </si>
   <si>
     <t xml:space="preserve">chara</t>
